--- a/kms_import_template.xlsx
+++ b/kms_import_template.xlsx
@@ -452,17 +452,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -478,30 +474,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Visibility</t>
+          <t>Workspace Dimension</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Dimension</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Functional Topic</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Property 4</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
@@ -520,30 +496,10 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>workspace</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>methodological</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Human Resources</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>HR-SOP</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>HR, SOP, Onboarding</t>
         </is>
@@ -562,30 +518,10 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>workspace</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>IT Infrastructure</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Dev-SOP</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+          <t>it</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>IT, Guide, Technical</t>
         </is>
@@ -599,37 +535,39 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;Ý tưởng Chiến dịch Truyền thông Quý 3&lt;/h2&gt;&lt;p&gt;Tài liệu nháp cá nhân về ý tưởng phát triển kênh Tiktok của công ty.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Lưu ý: Đây là tài liệu bảo mật cá nhân, chỉ chia sẻ khi được duyệt phác thảo.&lt;/em&gt;&lt;/p&gt;</t>
+          <t>&lt;h2&gt;Ý tưởng Chiến dịch Truyền thông Quý 3&lt;/h2&gt;&lt;p&gt;Tài liệu nháp cá nhân về ý tưởng phát triển chiến dịch truyền thông bán hàng.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Lưu ý: Đây là tài liệu bảo mật cá nhân, chỉ chia sẻ khi được duyệt phác thảo.&lt;/em&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>private</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>individual</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>strategic</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Marketing-Draft</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Marketing, Idea, Confidential</t>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Sales, Idea, Marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>OPS-004: Quy trình Vận hành Máy chủ và Backup</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Quy trình Vận hành Máy chủ&lt;/h2&gt;&lt;p&gt;Quy trình kiểm tra định kỳ tình trạng hệ thống và backup dữ liệu.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>ops</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Ops, Guide, Backup</t>
         </is>
       </c>
     </row>

--- a/kms_import_template.xlsx
+++ b/kms_import_template.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="KMS Import Template" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,32 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -58,35 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,122 +413,159 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Workspace Dimension</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>HR-001: Quy trình Bàn giao Công việc khi Nghỉ việc</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>&lt;h2&gt;Quy trình Bàn giao Công việc&lt;/h2&gt;&lt;p&gt;Tài liệu này hướng dẫn các bước nhân viên cần thực hiện khi xin nghỉ việc tại công ty.&lt;/p&gt;&lt;h3&gt;Các bước chi tiết:&lt;/h3&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Bước 1:&lt;/strong&gt; Gửi thông báo nghỉ việc chính thức trước 30-45 ngày.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Bước 2:&lt;/strong&gt; Liệt kê danh sách công việc đang thực hiện và tài liệu liên quan.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Bước 3:&lt;/strong&gt; Chuyển giao quyền truy cập các tài khoản nghiệp vụ cho người tiếp quản.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Bước 4:&lt;/strong&gt; Ký biên bản bàn giao có xác nhận của Quản lý trực tiếp.&lt;/li&gt;&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>hr</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>HR, SOP, Onboarding</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Poor Payment History Customer</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Poor Payment History Customer Handling&lt;/h2&gt;&lt;p&gt;Customers with a poor payment history or recurring invoice delays must be handled strictly on a cash-only or immediate digital payment basis. Delayed billing, credit agreements, or check payments are strictly prohibited for these accounts. Employees must politely inform the customer of this requirement and process payments immediately. In case of customer dispute or complaints, escalate the matter to the Sales Manager.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sales, Policy, Payment</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>IT-002: Hướng dẫn Cài đặt Môi trường Làm việc cho Dev</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>&lt;h2&gt;Hướng dẫn cài đặt môi trường&lt;/h2&gt;&lt;p&gt;Tài liệu hướng dẫn lập trình viên mới cấu hình máy tính cá nhân.&lt;/p&gt;&lt;h3&gt;Các phần mềm cần cài đặt:&lt;/h3&gt;&lt;ol&gt;&lt;li&gt;Git và cấu hình SSH key truy cập GitLab của công ty.&lt;/li&gt;&lt;li&gt;Docker Desktop và cấu hình Docker Compose.&lt;/li&gt;&lt;li&gt;VS Code hoặc PyCharm tùy theo dự án.&lt;/li&gt;&lt;li&gt;Cài đặt Python 3.10+ hoặc Node.js 18+.&lt;/li&gt;&lt;/ol&gt;</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>IT, Guide, Technical</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VIP Customer Privileges</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;VIP Customer Privileges and Discounts&lt;/h2&gt;&lt;p&gt;VIP customers are entitled to priority reservation, dedicated seating, and a standard 10% discount on all dine-in orders. For VIP customer orders exceeding a total of $100, the Front-of-House (FOH) supervisor can approve an upgraded discount of 15%. This discount must be logged in the POS system under the VIP discount category.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sales, VIP, Discount</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>MKT-003: Ý tưởng Chiến dịch Truyền thông Quý 3</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>&lt;h2&gt;Ý tưởng Chiến dịch Truyền thông Quý 3&lt;/h2&gt;&lt;p&gt;Tài liệu nháp cá nhân về ý tưởng phát triển chiến dịch truyền thông bán hàng.&lt;/p&gt;&lt;p&gt;&lt;em&gt;Lưu ý: Đây là tài liệu bảo mật cá nhân, chỉ chia sẻ khi được duyệt phác thảo.&lt;/em&gt;&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Sales, Idea, Marketing</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>POS Pricing Fixes</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;POS Pricing Fixes Procedure&lt;/h2&gt;&lt;p&gt;In the event of a pricing error or incorrect display in the POS system during customer checkout, cashiers must stop the transaction immediately and notify the Front-of-House (FOH) Supervisor. The supervisor will investigate the discrepancy and use their manager override key to manually correct the price on the POS interface. Under no circumstances should cashiers process incorrect pricing or attempt to override transactions without supervisor approval.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sales, POS, Technical</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>OPS-004: Quy trình Vận hành Máy chủ và Backup</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>&lt;h2&gt;Quy trình Vận hành Máy chủ&lt;/h2&gt;&lt;p&gt;Quy trình kiểm tra định kỳ tình trạng hệ thống và backup dữ liệu.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>ops</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Ops, Guide, Backup</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Recommended Time for Purchasing</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Recommended Time for Purchasing Inventory&lt;/h2&gt;&lt;p&gt;The recommended time for purchasing inventory is during the first week of every calendar month. Buying stock during this period allows FoodHub to secure bulk purchasing discounts from primary suppliers and ensures that all ingredients are received, checked, and shelved before the peak sales period mid-month.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Purchase, Procurement, Inventory</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Avoid Purchasing at Unusually Low Prices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Avoid Purchasing at Unusually Low Prices SOP&lt;/h2&gt;&lt;p&gt;Purchasing agents must avoid buying raw materials or inventory at unusually low prices. Suppliers offering items significantly below standard market rates often supply sub-standard quality ingredients, counterfeit goods, or products nearing their expiration dates. FoodHub maintains high food safety standards; all purchases below market price must be verified for origin and quality by the Quality Assurance (QA) team.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Purchase, Supplier, Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Preventing Missing or Incorrect Item Deliveries</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Preventing Missing or Incorrect Item Deliveries&lt;/h2&gt;&lt;p&gt;To prevent missing or incorrect items in deliveries, kitchen staff must perform a double-check of the packed food against the printed order ticket before sealing the package. Once verified, a colored safety seal must be applied to the bag. Delivery drivers are required to verify the delivery address and order ID on their mobile app upon arrival and during handoff to the customer.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Helpdesk, Delivery, Kitchen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Customer Complaint Handling</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;Customer Complaint Handling Guidelines&lt;/h2&gt;&lt;p&gt;When handling customer complaints, employees must listen actively, maintain a professional and empathetic tone, apologize for the inconvenience, and offer an immediate resolution (such as a replacement item, a full refund, or a store credit voucher). If the customer remains dissatisfied or the complaint involves food safety issues, immediately escalate the case to the shift manager on duty.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Front-of-House, Customer Service, SOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>POS System Troubleshooting Guide</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;POS System Troubleshooting Guide&lt;/h2&gt;&lt;p&gt;If the POS system is not responding or becomes frozen, follow these steps: first, verify that all power cables and network cables are securely connected. Second, perform a soft reboot by pressing and holding the power button for 5 seconds. If the system fails to restart or respond after rebooting, contact the IT Helpdesk immediately and switch to using the manual receipt book to record transactions.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Technical, IT, Troubleshooting</t>
         </is>
       </c>
     </row>
